--- a/Data/Output/capitals_enriched.xlsx
+++ b/Data/Output/capitals_enriched.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1081</v>
+        <v>3105</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5131</v>
+        <v>2089</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6073</v>
+        <v>5071</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3108</v>
+        <v>7078</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4078</v>
+        <v>6157</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7093</v>
+        <v>4068</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2069</v>
+        <v>1061</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7690</v>
+        <v>7594</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8006</v>
+        <v>8014</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_enriched.xlsx
+++ b/Data/Output/capitals_enriched.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3105</v>
+        <v>1062</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2089</v>
+        <v>2060</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5071</v>
+        <v>6057</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7078</v>
+        <v>5059</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6157</v>
+        <v>7063</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4068</v>
+        <v>3056</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1061</v>
+        <v>4054</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7594</v>
+        <v>7681</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8014</v>
+        <v>7997</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_enriched.xlsx
+++ b/Data/Output/capitals_enriched.xlsx
@@ -393,7 +393,7 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>distance_road_km</t>
+          <t>distance_road</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1062</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2060</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6057</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5059</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7063</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3056</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4054</v>
+        <v>43</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7681</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7997</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_enriched.xlsx
+++ b/Data/Output/capitals_enriched.xlsx
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/capitals_enriched.xlsx
+++ b/Data/Output/capitals_enriched.xlsx
@@ -1671,20 +1671,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1794,7 +1780,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1846,7 +1832,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1898,7 +1884,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1950,7 +1936,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2002,7 +1988,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2054,7 +2040,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2106,7 +2092,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2158,7 +2144,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2210,7 +2196,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2262,7 +2248,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
